--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260511_211027.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260511_211027.xlsx
@@ -4206,7 +4206,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260511_211027.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260511_211027.xlsx
@@ -5772,7 +5772,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260511_211027.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260511_211027.xlsx
@@ -4206,7 +4206,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260511_211027.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260511_211027.xlsx
@@ -4206,7 +4206,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5772,7 +5772,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260511_211027.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260511_211027.xlsx
@@ -4206,7 +4206,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5772,7 +5772,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260511_211027.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260511_211027.xlsx
@@ -5772,7 +5772,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260511_211027.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260511_211027.xlsx
@@ -4206,7 +4206,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5772,7 +5772,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260511_211027.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260511_211027.xlsx
@@ -4206,7 +4206,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5772,7 +5772,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
